--- a/forms/templates/interactive-board.xlsx
+++ b/forms/templates/interactive-board.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\FormSite\forms\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C8F6BE4-D451-4E00-A0B8-C450CC7FACD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE061478-3CBB-4718-8B96-80EDBAF33006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -92,9 +92,6 @@
     <t>Тимчасово виконуючий обов'язки командира військової частини А2896</t>
   </si>
   <si>
-    <t>полковник                                                                                                                                                                      Ігор ХАРЧЕНКО</t>
-  </si>
-  <si>
     <t>Інтерактивна панель командного пункту</t>
   </si>
   <si>
@@ -108,6 +105,9 @@
   </si>
   <si>
     <t>Сорока Юхим Геннадійович</t>
+  </si>
+  <si>
+    <t>полковник</t>
   </si>
 </sst>
 </file>
@@ -225,20 +225,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -273,9 +264,6 @@
     <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -288,6 +276,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -297,17 +288,17 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1445,220 +1436,219 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="10"/>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="11" t="s">
+      <c r="A1" s="7"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="8" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="12"/>
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="9"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="15"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="12"/>
     </row>
     <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
     </row>
     <row r="8" spans="1:6" ht="24.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="22" t="s">
+      <c r="D8" s="20"/>
+      <c r="E8" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="23"/>
+      <c r="F8" s="20"/>
     </row>
     <row r="9" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="23"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="16" t="s">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="13" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="24" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="7"/>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="4"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
     </row>
     <row r="13" spans="1:6" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="13" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="55.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="28" t="s">
+      <c r="B14" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="21" t="s">
-        <v>24</v>
+      <c r="F14" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="24"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="1"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="25" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
+      <c r="A18" s="24"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
       <c r="F18" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A7:F7"/>
@@ -1666,6 +1656,8 @@
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="E8:F8"/>
+    <mergeCell ref="A17:E18"/>
+    <mergeCell ref="F17:F18"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C14" r:id="rId1" xr:uid="{A6A91D78-91F3-4DB6-8132-4C1AAD2897FE}"/>

--- a/forms/templates/interactive-board.xlsx
+++ b/forms/templates/interactive-board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\FormSite\forms\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE061478-3CBB-4718-8B96-80EDBAF33006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14ECBBFE-2371-4D9B-98A4-A43618B6C455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
   <si>
     <t>Додаток 1</t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>Сорока Юхим Геннадійович</t>
+  </si>
+  <si>
+    <t>Ігор ХАРЧЕНКО</t>
   </si>
   <si>
     <t>полковник</t>
@@ -225,7 +228,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -297,8 +300,11 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1625,28 +1631,21 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="84" x14ac:dyDescent="0.3">
       <c r="A17" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
       <c r="F17" s="25" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="24"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="25"/>
+      <c r="A18" s="26" t="s">
+        <v>29</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="9">
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="A4:F4"/>
@@ -1656,8 +1655,6 @@
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="E8:F8"/>
-    <mergeCell ref="A17:E18"/>
-    <mergeCell ref="F17:F18"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C14" r:id="rId1" xr:uid="{A6A91D78-91F3-4DB6-8132-4C1AAD2897FE}"/>

--- a/forms/templates/interactive-board.xlsx
+++ b/forms/templates/interactive-board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\FormSite\forms\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14ECBBFE-2371-4D9B-98A4-A43618B6C455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{969230D4-6400-4D7E-8B25-1DAFD8873374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -298,7 +298,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1631,10 +1631,14 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
-    <row r="17" spans="1:6" ht="84" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="24" t="s">
         <v>22</v>
       </c>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
       <c r="F17" s="25" t="s">
         <v>28</v>
       </c>
@@ -1645,7 +1649,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="A4:F4"/>
@@ -1655,6 +1659,7 @@
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="E8:F8"/>
+    <mergeCell ref="A17:E17"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C14" r:id="rId1" xr:uid="{A6A91D78-91F3-4DB6-8132-4C1AAD2897FE}"/>
